--- a/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T08:38:22+00:00</t>
+    <t>2024-09-24T14:40:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-24T14:40:25+00:00</t>
+    <t>2024-09-25T08:38:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T08:38:03+00:00</t>
+    <t>2024-09-25T13:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/92-accueil-mettre-à-jour-le-descriptif-pour-présenter-le-cas-dusage-ssiad-dans-les-données-techniques/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-25T13:06:15+00:00</t>
+    <t>2024-09-25T13:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
